--- a/Apostas_Diarias/Apostas_20260509.xlsx
+++ b/Apostas_Diarias/Apostas_20260509.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_65A9ED4295A6C634B541C8F0505ED87656CD94C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF382F3-A655-43F0-9BE3-0755BF395713}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_65A9ED4295A6C634B541C8F0505ED87656CD94C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E5C834F-13A7-4FEA-AAFD-741E8724A770}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Data</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>Konyaspor x Fenerbahce</t>
+  </si>
+  <si>
+    <t>1/0</t>
   </si>
 </sst>
 </file>
@@ -223,6 +226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,8 +607,8 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1">
-        <v>500</v>
+      <c r="V1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
